--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0162.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0162.xlsx
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Hừ! Ta không sợ! Ta chỉ… lo có kẻ khác cướp mất thuốc tiên trước thôi!</t>
+          <t>Hừ! Tao không sợ! Tao chỉ… lo có kẻ khác cướp mất thuốc tiên trước thôi!</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Meo!</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>&lt;te href=800003&gt;Second Coming of Solaris&lt;/te&gt;! Chúc mừng tròn một năm thử nghiệm beta!</t>
+          <t>&lt;te href=800003&gt;Lần Trở Lại Của Solaris&lt;/te&gt;! Chúc mừng tròn một năm thử nghiệm beta!</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Bắt đầu thôi nào! Tethys à? Nghe thấy ta không? Mọi thứ đã sẵn sàng rồi!</t>
+          <t>Bắt đầu thôi nào! Tethys à? Nghe thấy tao không? Mọi thứ đã sẵn sàng rồi!</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Thảm Họa Tái Diễn! &lt;te href=800003&gt;Second Coming of Solaris&lt;/te&gt; giờ đây đang hỗn loạn!</t>
+          <t>Thảm Họa Tái Diễn! &lt;te href=800003&gt;Solaris Trở Lại&lt;/te&gt; giờ đây đang hỗn loạn!</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Được! Vậy thì ta giao việc này cho ngươi, {PlayerName}. Ngươi làm được mà—Encore tin tưởng ngươi!</t>
+          <t>Được! Vậy thì tao giao việc này cho mày, {PlayerName}. Mày làm được mà—Encore tin tưởng mày!</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Ta có thể tự đánh bại ngươi, Abbowser!</t>
+          <t>Tao có thể tự đánh bại mày, Abbowser!</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Giờ ta sẽ cho ngươi vài Khối Lập Phương làm đồng đội đầu tiên. Không phải ta ném ngươi vào chỗ chết đâu... muahaha!</t>
+          <t>Giờ tao sẽ cho mày vài Khối Lập Phương làm đồng đội đầu tiên. Không phải tao ném mày vào chỗ chết đâu... muahaha!</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Hừ, lo cho bản thân đi! Là Đại Ca đây, ta sẽ cho ngươi thấy ta thực sự là ai!</t>
+          <t>Hừ, lo cho bản thân đi! Là Đại Ca đây, tao sẽ cho mày thấy tao thực sự là ai!</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Bạn có đang vui không?</t>
+          <t>Cậu đang vui chứ?</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Không, không phải ta đâu!</t>
+          <t>Không, không phải tao đâu!</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Nghe ta nói không? Đến sau... nhưng đừng quá muộn nhé! Dù sao cũng phải đến tìm ta đấy. Ta sẽ đợi!</t>
+          <t>Nghe tao nói không? Đến sau... nhưng đừng quá muộn nhé! Dù sao cũng phải đến tìm tao đấy. Tao sẽ đợi!</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Baa! Nhiều &lt;te href=800004&gt;Cube&lt;/te&gt; quá!</t>
+          <t>Baa! Nhiều &lt;te href=800004&gt;Khối Lập Phương&lt;/te&gt; quá!</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Encore?</t>
+          <t>Encore à?</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Không cần khách sáo thế đâu. Cả hai danh xưng "vị khách quý" và "ân nhân của Kim Châu" đều thuộc về cậu, {PlayerName}. Ta sẽ luôn dốc hết sức để hỗ trợ cậu.</t>
+          <t>Không cần khách sáo thế đâu. Cả hai danh xưng "vị khách quý" và "ân nhân của Jinzhou" đều thuộc về cậu, {PlayerName}. Ta sẽ luôn dốc hết sức để hỗ trợ cậu.</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Nhưng còn cậu thì sao, {PlayerName}? Sau khi rời Kim Châu... và trước khi trở lại...</t>
+          <t>Nhưng còn cậu thì sao, {PlayerName}? Sau khi rời Jinzhou... và trước khi trở lại...</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Quay lại vấn đề chính nào. {PlayerName}, thế giới này gọi là &lt;te href=800003&gt;Second Coming of Solaris&lt;/te&gt;, phải không?</t>
+          <t>Quay lại vấn đề chính nào. {PlayerName}, thế giới này gọi là &lt;te href=800003&gt;Solaris Trở Lại&lt;/te&gt;, phải không?</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Được rồi, cách này thế này. Cậu có thể làm một bản CV nhóm, rồi ta sẽ lo giới thiệu nội bộ cho.</t>
+          <t>Được rồi, cách này thế này. Cậu có thể làm một bản CV nhóm, rồi tao sẽ lo giới thiệu nội bộ cho.</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Rồi mấy tên Đặc sứ đến bắt ta, nhưng ta cứ hát suốt trong lúc chúng đuổi theo!</t>
+          <t>Rồi mấy tên Đặc sứ đến bắt tao, nhưng tao cứ hát suốt trong lúc chúng đuổi theo!</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Không. Giống như những &lt;te href=800004&gt;Cube&lt;/te&gt; khác, ta hoàn toàn tách biệt với bản thể thật của mình.</t>
+          <t>Không. Giống như những &lt;te href=800004&gt;Khối Dư Dả&lt;/te&gt; khác, ta hoàn toàn tách biệt với bản thể thật của mình.</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Đúng vậy. Ngài Chỉ Huy Trưởng mới bảo chúng tôi "r?i ?i," nên chúng tôi đến đây—trạm sạc, nơi có nhiều tiếng vo ve nhất, cũng hợp lệnh mà nhỉ.</t>
+          <t>Đúng vậy. Ngài Chỉ Huy Trưởng mới bảo chúng tôi "cút đi," nên chúng tôi đến đây—trạm sạc, nơi có nhiều tiếng vo ve nhất, cũng hợp lệnh mà nhỉ.</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Ta có linh cảm không lành về chuyện này...</t>
+          <t>Tao có linh cảm không lành về chuyện này...</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Nếu ta giúp xây dựng Bờ Đen Mới này, sẽ dễ bắt được Ngươi hơn đấy!</t>
+          <t>Nếu tao giúp xây dựng Bờ Đen Mới này, sẽ dễ bắt được MÀY hơn đấy!</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Biến đi cho rồi! Đừng có phá đám ta với {PlayerName}!</t>
+          <t>Biến đi cho rồi! Đừng có phá đám tao với {PlayerName}!</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Im nào, đồ nhóc! Ta sẽ không để ai cản trở giờ chơi với thủ lĩnh yêu quý của ta đâu.</t>
+          <t>Im nào, đồ nhóc! Tao sẽ không để ai cản trở giờ chơi với thủ lĩnh yêu quý của tao đâu.</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Vậy đây chính là &lt;te href=800003&gt;Second Coming of Solaris&lt;/te&gt; sao... Không, ngay cả trong trò chơi, điều này cũng quá...</t>
+          <t>Vậy đây chính là &lt;te href=800003&gt;Lần Trở Lại Thứ Hai của Solaris&lt;/te&gt; sao... Không, ngay cả trong trò chơi, điều này cũng quá...</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Chết tiệt! Ngươi mở cái rương ta chuẩn bị cho {PlayerName} rồi à?</t>
+          <t>Chết tiệt! Mày mở cái rương tao chuẩn bị cho {PlayerName} rồi à?</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Đồ trộm cắp! Ta sẽ nhốt ngươi lại... Khoan, cái rương này sao to thế này? To quá đi!</t>
+          <t>Đồ trộm cắp! Tao sẽ nhốt mày lại... Khoan, cái rương này sao to thế này? To quá đi!</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Rương... xoay... rương... Ugh, đầu ta choáng váng quá.</t>
+          <t>Rương... xoay... rương... Ugh, đầu tao choáng váng quá.</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Trước khi nhốt một kẻ vô danh như ta lại, sao không mở cái rương trước đi?</t>
+          <t>Trước khi nhốt một kẻ vô danh như tao lại, sao không mở cái rương trước đi?</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Đúng rồi! Đến tay ta đây, cái rương khổng lồ kia!</t>
+          <t>Đúng rồi! Đến tay tao đây, cái rương khổng lồ kia!</t>
         </is>
       </c>
     </row>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Tôi có thể xác nhận là {Male=anh;Female=chị} {PlayerName} hạ gục chúng mà chẳng hề toát mồ hôi.</t>
+          <t>Tôi có thể xác nhận là {Male=Mr.;Female=Ms.} {PlayerName} hạ gục chúng mà chẳng hề toát mồ hôi.</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Cảm ơn, nhưng chưa phải lúc. {Male=Ông;Female=Bà} Mắt Mèo của chúng ta đang cần giúp đỡ. Đến lượt tôi đền đáp {Male=ông ấy;Female=bà ấy}.</t>
+          <t>Cảm ơn, nhưng chưa phải lúc. {Male=him;Female=her} Mắt Mèo của chúng ta đang cần giúp đỡ. Đến lượt tôi đền đáp {Male=him;Female=her}.</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Ta biết rằng tầng này còn chứa vài &lt;te href=800004&gt;Cube&lt;/te&gt; khác bị Abbowser chiếm giữ. Chúng ta sẽ cùng nhau tìm ra chúng.</t>
+          <t>Ta biết rằng tầng này còn chứa vài &lt;te href=800004&gt;Khối Lập Phương&lt;/te&gt; khác bị Abbowser chiếm giữ. Chúng ta sẽ cùng nhau tìm ra chúng.</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Ta không ngờ cậu lại có tham vọng như vậy đấy, Phoebe.</t>
+          <t>Tao không ngờ cậu lại có tham vọng như vậy đấy, Phoebe.</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Thôi nào, Primus. Nếu không có sự dẫn dắt của anh, chúng ta vẫn chỉ là những &lt;te href=800004&gt;Cube&lt;/te&gt; lạc lối, lang thang! Anh chính là vị cứu tinh của chúng ta!</t>
+          <t>Thôi nào, Primus. Nếu không có sự dẫn dắt của anh, chúng ta vẫn chỉ là những &lt;te href=800004&gt;Khối Lập Phương&lt;/te&gt; lạc lối, lang thang! Anh chính là vị cứu tinh của chúng ta!</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Không. Không đời nào! Ta không cần Sentinel! Chúng ta muốn Phoebe! Ngươi sẽ không bao giờ cướp được Primus khỏi tay chúng ta đâu!</t>
+          <t>Không. Không đời nào! Tao không cần Sentinel! Chúng tao muốn Phoebe! Mày sẽ không bao giờ cướp được Primus khỏi tay chúng tao đâu!</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Còn bạn là...?</t>
+          <t>Và ngươi là?</t>
         </is>
       </c>
     </row>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>{PlayerName}, nếu cậu đến vì cái rương này, cứ lấy đi. Abbowser còn nợ lương chúng ta, nên chẳng có nghĩa vụ gì phải giữ nó cả.</t>
+          <t>{PlayerName}, nếu cậu đến vì cái rương này, cứ lấy đi. Abbowser còn nợ lương chúng tao, nên chẳng có nghĩa vụ gì phải giữ nó cả.</t>
         </is>
       </c>
     </row>
